--- a/НИР_ЭДО_7стран_и_практика/05_Матрицы/Анализ_судебной_практики_ЭДО.xlsx
+++ b/НИР_ЭДО_7стран_и_практика/05_Матрицы/Анализ_судебной_практики_ЭДО.xlsx
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -598,6 +598,7 @@
     <col width="52" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -638,7 +639,12 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Ссылка</t>
+          <t>Ссылка 1 (проверить)</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Ссылка 2 (проверить)</t>
         </is>
       </c>
     </row>
@@ -683,6 +689,11 @@
           <t>https://www.bundesgerichtshof.de/SharedDocs/Entscheidungen/DE/Zivilsenate/VIII_ZS/2023/VIII_ZR_155-23.pdf?__blob=publicationFile&amp;v=1</t>
         </is>
       </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>https://rewis.io/urteile/urteil/wfg-27-11-2024-viii-zr-15523/</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="92" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -725,6 +736,11 @@
           <t>https://zakony-by.com/hozyajstvennyj_protsessualnyj_kodeks_rb/84.htm</t>
         </is>
       </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>https://bii.by/docs/ispolzovanie-dokumentov-v-elektronnom-vide-v-dogovornykh-otnosheniyakh-sudebnaya-praktika-358365</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="92" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -767,6 +783,11 @@
           <t>https://www.prlegal.rs/filing-a-complaint-via-email-yes-it-is-possible/</t>
         </is>
       </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prlegal.rs/electronic-signing-of-documents-in-serbia-novelties-in-signing-of-financial-statements-for-business-registers-agency/</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="92" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -809,6 +830,11 @@
           <t>https://www.boe.es/eli/es/l/2020/11/11/6</t>
         </is>
       </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>https://www.legaltoday.com/practica-juridica/derecho-penal/valor-probatorio-de-los-pantallazos-de-conversaciones-de-whatsapp-o-sus-transcripciones-sts-116-2025-de-13-de-febrero-2025-09-29/</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="92" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -851,6 +877,11 @@
           <t>https://www.bailii.org/ie/cases/IEHC/2010/H47.html</t>
         </is>
       </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>https://www.irishstatutebook.ie/eli/2000/act/27/section/9/enacted/en/html</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="92" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -893,6 +924,11 @@
           <t>https://www.legalis.net/jurisprudences/cour-de-cassation-civile-ch-civile-3-arret-du-5-mars-2026/</t>
         </is>
       </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>https://www.doctrine.fr/d/CASS/2026/CASSP5F27671B4851EF0B45AF</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="92" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -935,6 +971,11 @@
           <t>https://new.kenyalaw.org/akn/ke/judgment/keelc/2025/392/eng@2025-02-06</t>
         </is>
       </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>https://new.kenyalaw.org/akn/ke/doc/newsletter/2025-05-12/kenya-law-weekly-issue-04224-25/eng@2025-05-12</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="92" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -975,19 +1016,32 @@
       <c r="H9" s="6" t="inlineStr">
         <is>
           <t>https://www.consultant.ru/document/cons_doc_LAW_181602/</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_112701/</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
